--- a/dialogue.xlsx
+++ b/dialogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noorb\Documents\GitHub\Nut-Digger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E48CC50-2829-4194-A5C0-F395A13AC038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77411710-41DC-4D86-BE54-7D896E3596B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{5407D05E-54CC-46DD-837F-C8BB1BCABA22}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
   <si>
     <t>name</t>
   </si>
@@ -156,6 +156,24 @@
   </si>
   <si>
     <t>("Oh dear, uhm, how can I say this nicely...", "Jeez louise, okay let's do it!", "What a lovely surprise, of course!")</t>
+  </si>
+  <si>
+    <t>Shopkeeper</t>
+  </si>
+  <si>
+    <t>What's up?</t>
+  </si>
+  <si>
+    <t>Oh no you're cut off buddy. No more bets until you've repaid your debt.</t>
+  </si>
+  <si>
+    <t>I want to bet, money tips?</t>
+  </si>
+  <si>
+    <t>"You know I heard about a golden ring in the dark forest, I'll give you 1k nuts for it.","You get the ring yet brokie?"</t>
+  </si>
+  <si>
+    <t>"Wow I didn't think you'd actually go get it" -&gt; special trigger</t>
   </si>
 </sst>
 </file>
@@ -191,16 +209,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -546,6 +561,7 @@
     <col min="2" max="2" width="33.1796875" customWidth="1"/>
     <col min="3" max="3" width="31.26953125" customWidth="1"/>
     <col min="4" max="4" width="38.26953125" customWidth="1"/>
+    <col min="5" max="5" width="41.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -561,6 +577,9 @@
       <c r="D1" t="s">
         <v>9</v>
       </c>
+      <c r="E1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
@@ -575,6 +594,9 @@
       <c r="D2" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="E2" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
@@ -589,6 +611,9 @@
       <c r="D3" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="E3" s="1" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
@@ -597,7 +622,7 @@
       <c r="B4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -608,16 +633,18 @@
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
     </row>
@@ -676,6 +703,9 @@
       <c r="D9" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="E9" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
@@ -698,8 +728,15 @@
       <c r="B11" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>42</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dialogue.xlsx
+++ b/dialogue.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noorb\Documents\GitHub\Nut-Digger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77411710-41DC-4D86-BE54-7D896E3596B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF70E80-044C-49A7-B92E-3CBDD52F15F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{5407D05E-54CC-46DD-837F-C8BB1BCABA22}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{5407D05E-54CC-46DD-837F-C8BB1BCABA22}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Dialogue" sheetId="1" r:id="rId1"/>
+    <sheet name="Found text" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="67">
   <si>
     <t>name</t>
   </si>
@@ -174,14 +175,119 @@
   </si>
   <si>
     <t>"Wow I didn't think you'd actually go get it" -&gt; special trigger</t>
+  </si>
+  <si>
+    <t>incorrect answers</t>
+  </si>
+  <si>
+    <t>"I don't like sweets", "No, sorry"</t>
+  </si>
+  <si>
+    <t>"It's a secret","I like old squirrels"</t>
+  </si>
+  <si>
+    <t>"The indoors"</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>betting track</t>
+  </si>
+  <si>
+    <t>interaction prop</t>
+  </si>
+  <si>
+    <t>beetle</t>
+  </si>
+  <si>
+    <t>"beetle sounds"</t>
+  </si>
+  <si>
+    <t>outside the retirement homes</t>
+  </si>
+  <si>
+    <t>paper on tree</t>
+  </si>
+  <si>
+    <t>Francis house</t>
+  </si>
+  <si>
+    <t>Augusts house</t>
+  </si>
+  <si>
+    <t>Billies house</t>
+  </si>
+  <si>
+    <t>picture frame</t>
+  </si>
+  <si>
+    <t>"A family picture in front of a large lake"</t>
+  </si>
+  <si>
+    <t>hidden newspaper snippet</t>
+  </si>
+  <si>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Chef August's dessert bar awarded 2nd michelin star</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"</t>
+    </r>
+  </si>
+  <si>
+    <t>picture lying on table</t>
+  </si>
+  <si>
+    <t>"An old picture, Billie is wearing a suit and speaking on the phone"</t>
+  </si>
+  <si>
+    <t>"note to passerby: if Francis is lost again, tell him to look for the big arrow."</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -197,7 +303,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -205,11 +311,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -220,6 +335,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -554,7 +670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B6E0804-9C18-442D-8164-AAFA4ADAD369}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.54296875" customWidth="1"/>
@@ -690,55 +806,151 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B11" s="1">
         <v>4000</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C11" s="1">
         <v>11000</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D11" s="1">
         <v>7000</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
         <v>13</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C12" t="s">
         <v>13</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
         <v>13</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E12" t="s">
         <v>42</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F3D1FD7-5624-443C-86A7-B25899C382C7}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.453125" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="30.36328125" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.4">
+      <c r="A1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/dialogue.xlsx
+++ b/dialogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noorb\Documents\GitHub\Nut-Digger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF70E80-044C-49A7-B92E-3CBDD52F15F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD5FBB6-696F-4B53-80E7-E9617C53B5A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{5407D05E-54CC-46DD-837F-C8BB1BCABA22}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="75">
   <si>
     <t>name</t>
   </si>
@@ -171,9 +171,6 @@
     <t>I want to bet, money tips?</t>
   </si>
   <si>
-    <t>"You know I heard about a golden ring in the dark forest, I'll give you 1k nuts for it.","You get the ring yet brokie?"</t>
-  </si>
-  <si>
     <t>"Wow I didn't think you'd actually go get it" -&gt; special trigger</t>
   </si>
   <si>
@@ -222,17 +219,29 @@
     <t>Billies house</t>
   </si>
   <si>
-    <t>picture frame</t>
-  </si>
-  <si>
     <t>"A family picture in front of a large lake"</t>
   </si>
   <si>
     <t>hidden newspaper snippet</t>
   </si>
   <si>
+    <t>"note to passerby: if Francis is lost again, tell him to look for the big arrow."</t>
+  </si>
+  <si>
+    <t>"You know I heard about a golden ring in the dark forest, I'll give you 1k nuts for it, or you can use it to marry some rich idiot hahaha","You get the ring yet brokie?"</t>
+  </si>
+  <si>
+    <t>Large picture frame</t>
+  </si>
+  <si>
+    <t>hiking gear on the wall</t>
+  </si>
+  <si>
+    <t>"Hiking gear, it looks expensive"</t>
+  </si>
+  <si>
     <r>
-      <t>"</t>
+      <t xml:space="preserve">"1980: </t>
     </r>
     <r>
       <rPr>
@@ -257,13 +266,28 @@
     </r>
   </si>
   <si>
-    <t>picture lying on table</t>
-  </si>
-  <si>
-    <t>"An old picture, Billie is wearing a suit and speaking on the phone"</t>
-  </si>
-  <si>
-    <t>"note to passerby: if Francis is lost again, tell him to look for the big arrow."</t>
+    <t>teaset next to couch</t>
+  </si>
+  <si>
+    <t>"A fine china teaset, the cups have golden rims"</t>
+  </si>
+  <si>
+    <t>pipe</t>
+  </si>
+  <si>
+    <t>picture on the wall</t>
+  </si>
+  <si>
+    <t>"An old picture, a serious Billie is wearing a suit and speaking on the phone"</t>
+  </si>
+  <si>
+    <t>"A strange pipe"</t>
+  </si>
+  <si>
+    <t>meds on the table</t>
+  </si>
+  <si>
+    <t>"Some Voltaren and Ibuprofen"</t>
   </si>
 </sst>
 </file>
@@ -759,7 +783,7 @@
         <v>26</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -808,16 +832,16 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
@@ -834,7 +858,7 @@
         <v>38</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -875,7 +899,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F3D1FD7-5624-443C-86A7-B25899C382C7}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.453125" customWidth="1"/>
@@ -885,68 +909,112 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s">
         <v>53</v>
-      </c>
-      <c r="C2" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="C3" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/dialogue.xlsx
+++ b/dialogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noorb\Documents\GitHub\Nut-Digger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD5FBB6-696F-4B53-80E7-E9617C53B5A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2629F8DC-AD84-476D-8FA6-94A2AE6DB32A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{5407D05E-54CC-46DD-837F-C8BB1BCABA22}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="78">
   <si>
     <t>name</t>
   </si>
@@ -288,6 +288,15 @@
   </si>
   <si>
     <t>"Some Voltaren and Ibuprofen"</t>
+  </si>
+  <si>
+    <t>On  entering dark forest</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>"So the 'dark forest' name is pretty litteral huh, maybe the locals have some fireflies I can use"</t>
   </si>
 </sst>
 </file>
@@ -899,10 +908,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F3D1FD7-5624-443C-86A7-B25899C382C7}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.453125" customWidth="1"/>
+    <col min="1" max="1" width="20.36328125" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="30.36328125" style="1" customWidth="1"/>
   </cols>
@@ -1017,6 +1026,17 @@
         <v>74</v>
       </c>
     </row>
+    <row r="13" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
